--- a/docs/工作簿1.xlsx
+++ b/docs/工作簿1.xlsx
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>也就是说在有炸矛/电矛拾荒者的情况下的灵活收益，道德低的话可以背刺</t>
+          <t>也就是说在有炸矛/电矛拾荒者的情况下的灵活收益，道德低的话可以背刺；好感度：给拾荒者珍珠+1、击杀-1，好感度&gt;0时任何拾荒者不攻击你（给珍珠时提示，攻击后播报高/低好感度）。</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>【雇佣】拾荒者在你手牌但攻击作用对面，无武器会拾取你的矛</t>
+          <t>【雇佣】拾荒者在你手牌但攻击作用对面，无武器会拾取你的矛；给珍珠雇佣同样+1好感度。</t>
         </is>
       </c>
     </row>
